--- a/Data/19_ADAS_sensor_adoption.xlsx
+++ b/Data/19_ADAS_sensor_adoption.xlsx
@@ -13,9 +13,8 @@
     <sheet name="Tier_Shares" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Lidar" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Presence_per_Tier" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Uncertainty" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Validation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Uncertainty" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Validation" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -102,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,7 +124,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -2435,13 +2433,15 @@
       <c r="E10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="10">
-        <f>Driver B</f>
-        <v/>
-      </c>
-      <c r="G10" s="10">
-        <f>Driver B</f>
-        <v/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Driver B</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Driver B</t>
+        </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
@@ -2661,232 +2661,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="62" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Driver C - post-2040 sensor-count scenarios - report S7.2 / S7.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>A wiring model needs to know HOW MANY sensors, not WHICH. The count after 2040 is set by two observable mechanisms: (1) cost decline with volume - by ~2040-45 sensor cost is negligible against vehicle price, so cost stops constraining count; (2) safety redundancy - once cost is not binding, required redundancy sets the count. A new sensor modality, if one arrives, simply appears as 'more sensors'. This REPLACES the withdrawn rule E4 ('no new modality before 2070'), which assumed zero over 45 years against a historical rate of roughly one new modality every 10-15 years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Active_Scenario</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>SAMPLE</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>SAMPLE = draw a scenario per iteration by weight; ONE run, and the band contains all three. This is the honest default and is what should be quoted. S1 / S2 / S3 = pin every iteration to that scenario, for comparing them as separate answers; outputs then take a _S1 / _S2 / _S3 suffix so runs cannot overwrite each other. SCENARIO_OVERRIDE in BevWiring.py section 0 beats this cell, for scripted sweeps.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Multiplier anchors (PCHIP through these; add or delete year columns freely)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Mechanism</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Cost-driven convergence</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Sensors get cheap, but sensing converges on a minimal efficient set (camera + radar). Redundancy achieved in compute, not hardware. The vision-only thesis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Regulated redundancy</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Cost decline makes redundancy affordable; L3/L4 type approval requires independent modality redundancy for fail-operational behaviour. MODE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Full fail-operational</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Private L4 requires dual-redundant sensing across every modality plus degraded-mode operation. Each sensing function duplicated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Weights sum (V10, must be 1.000)</t>
-        </is>
-      </c>
-      <c r="G12" s="12">
-        <f>SUM(G9:G11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="O14" s="15" t="inlineStr">
-        <is>
-          <t>All three scenarios are 1.00 at 2040 BY CONSTRUCTION, so Driver C cannot perturb any year for which sourced data exists (validation V9). Before 2040 the scenarios are identical and this driver has no effect.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>The band WIDENS after ~2045 by construction. That is deliberate: uncertainty about 2070 should exceed uncertainty about 2035. The withdrawn E4 made it narrow into the far future, which was the clearest sign it was wrong.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2981,12 +2755,12 @@
           <t>&gt;50%</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>1.6x</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>Two top-tier houses, same quantity, same year. Sets the floor for any 10-year-out forecast band.</t>
         </is>
@@ -3018,12 +2792,12 @@
           <t>4.6</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>1.20x</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Our tier table is deliberately conservative on the late ramp.</t>
         </is>
@@ -3055,12 +2829,12 @@
           <t>15 y</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>5 y</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>Confirms +/-5 y is the right order for the Driver A band.</t>
         </is>
@@ -3092,12 +2866,12 @@
           <t>60.3 kg</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>6.9%</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Two readings of the SAME source.</t>
         </is>
@@ -3129,12 +2903,12 @@
           <t>3546 m</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>2.8%</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>A single source disagreeing WITH ITSELF. Sets the noise floor: nothing here can claim better than ~3%.</t>
         </is>
@@ -3166,12 +2940,12 @@
           <t>-44/-40/-23%</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>3-4x</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>Largest spread in the whole chain. Structural, not statistical.</t>
         </is>
@@ -3203,12 +2977,12 @@
           <t>6 / 10</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>2x</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Within normal disagreement - NOT necessarily an error.</t>
         </is>
@@ -3240,12 +3014,12 @@
           <t>0.01</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>50x</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>FAR outside every band above. This one IS an error.</t>
         </is>
@@ -3277,12 +3051,12 @@
           <t>0.90</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>3.6x</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Genuinely unknown. Width is honest, not lazy.</t>
         </is>
@@ -3318,7 +3092,7 @@
           <t>Self-consistency floor</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>~3%</t>
         </is>
@@ -3335,7 +3109,7 @@
           <t>Cross-house forecast spread, 10 y out</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>~1.6x</t>
         </is>
@@ -3352,7 +3126,7 @@
           <t>Structural / mechanism uncertainty</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>3-4x</t>
         </is>
@@ -3369,7 +3143,7 @@
           <t>Threshold for calling something an error</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>&gt;10x</t>
         </is>
@@ -3385,7 +3159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3480,8 +3254,8 @@
           <t>existing anchor</t>
         </is>
       </c>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="19" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -3509,8 +3283,8 @@
           <t>17_ / 06_</t>
         </is>
       </c>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="20" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="G6" s="19" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -3538,8 +3312,8 @@
           <t>report S2.2 measured</t>
         </is>
       </c>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
+      <c r="F7" s="19" t="n"/>
+      <c r="G7" s="19" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -3567,8 +3341,8 @@
           <t>report S4.1 vs Yole 2.5</t>
         </is>
       </c>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="19" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -3596,8 +3370,8 @@
           <t>report S2.4</t>
         </is>
       </c>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -3625,8 +3399,8 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -3654,8 +3428,8 @@
           <t>report S6.3</t>
         </is>
       </c>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -3683,8 +3457,8 @@
           <t>interface doc S1</t>
         </is>
       </c>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -3712,8 +3486,8 @@
           <t>report S7.2</t>
         </is>
       </c>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -3741,8 +3515,8 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/19_ADAS_sensor_adoption.xlsx
+++ b/Data/19_ADAS_sensor_adoption.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Presence_per_Tier" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Uncertainty" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Validation" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Modules_vs_Elements" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -101,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -115,7 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -825,13 +825,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -844,72 +845,77 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>H3 and H4 are anchored on measured cars (EQS, i7, EX90). H0 is pinned by EU GSR-2. H1 and H2 are the weakest rows.</t>
+          <t>PER SEGMENT. Camera and radar counts are derived from 06_ composed through Presence_per_Tier, as MODULE counts (boxes needing a cable, not chips). H0 carries the GSR-2 legal floor: front camera AND driver-facing camera AND AEB radar. Ultrasonic scales with vehicle size.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Cam_min</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Cam_max</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Radar_min</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Radar_max</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Ultra_min</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Ultra_max</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Lidar_min</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Lidar_max</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Ranging_mode</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>SAE label seen</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
@@ -918,47 +924,52 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
           <t>H0</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>GSR-2 mandated floor</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>L0 / L1</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
@@ -967,145 +978,160 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>ACC + lane keeping</t>
         </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>hands-off highway</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="H7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>L2+</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>urban + highway 'L2++'</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="D8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>L2++ or L3</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>FACT-anchored</t>
         </is>
@@ -1114,47 +1140,592 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>redundant, liability transfer</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="D9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="F9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>FACT-anchored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>H0</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>GSR-2 mandated floor</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>L0 / L1</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>ACC + lane keeping</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>hands-off highway</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>L2+</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>urban + highway 'L2++'</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>L2++ or L3</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>FACT-anchored</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>redundant, liability transfer</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>FACT-anchored</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>H0</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>GSR-2 mandated floor</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>L0 / L1</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>ACC + lane keeping</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>hands-off highway</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I17" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>L2+</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>urban + highway 'L2++'</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" s="5" t="n">
+      <c r="G18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="5" t="n">
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>L2++ or L3</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>FACT-anchored</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>redundant, liability transfer</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="L19" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="N19" s="9" t="inlineStr">
         <is>
           <t>FACT-anchored</t>
         </is>
@@ -1250,26 +1821,26 @@
       <c r="B5" t="n">
         <v>2025</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="12">
+      <c r="F5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11">
         <f>SUM(C5:G5)</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f>C5*1.0+D5*2.0+E5*4.0+F5*5.3+G5*7.0</f>
         <v/>
       </c>
@@ -1283,26 +1854,26 @@
       <c r="B6" t="n">
         <v>2030</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12">
+      <c r="G6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11">
         <f>SUM(C6:G6)</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f>C6*1.0+D6*2.0+E6*4.0+F6*5.3+G6*7.0</f>
         <v/>
       </c>
@@ -1316,26 +1887,26 @@
       <c r="B7" t="n">
         <v>2035</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="G7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12">
+      <c r="G7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11">
         <f>SUM(C7:G7)</f>
         <v/>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <f>C7*1.0+D7*2.0+E7*4.0+F7*5.3+G7*7.0</f>
         <v/>
       </c>
@@ -1349,26 +1920,26 @@
       <c r="B8" t="n">
         <v>2040</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="10" t="n">
         <v>0.28</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <f>SUM(C8:G8)</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f>C8*1.0+D8*2.0+E8*4.0+F8*5.3+G8*7.0</f>
         <v/>
       </c>
@@ -1382,26 +1953,26 @@
       <c r="B9" t="n">
         <v>2050</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="11" t="n">
+      <c r="C9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <f>SUM(C9:G9)</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <f>C9*1.0+D9*2.0+E9*4.0+F9*5.3+G9*7.0</f>
         <v/>
       </c>
@@ -1415,26 +1986,26 @@
       <c r="B10" t="n">
         <v>2060</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="n">
+      <c r="C10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <f>SUM(C10:G10)</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <f>C10*1.0+D10*2.0+E10*4.0+F10*5.3+G10*7.0</f>
         <v/>
       </c>
@@ -1448,26 +2019,26 @@
       <c r="B11" t="n">
         <v>2070</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="11" t="n">
+      <c r="C11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <f>SUM(C11:G11)</f>
         <v/>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <f>C11*1.0+D11*2.0+E11*4.0+F11*5.3+G11*7.0</f>
         <v/>
       </c>
@@ -1481,26 +2052,26 @@
       <c r="B13" t="n">
         <v>2025</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="G13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
+      <c r="G13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11">
         <f>SUM(C13:G13)</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f>C13*1.0+D13*2.0+E13*4.0+F13*5.3+G13*7.0</f>
         <v/>
       </c>
@@ -1514,26 +2085,26 @@
       <c r="B14" t="n">
         <v>2030</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="10" t="n">
         <v>0.28</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <f>SUM(C14:G14)</f>
         <v/>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="12">
         <f>C14*1.0+D14*2.0+E14*4.0+F14*5.3+G14*7.0</f>
         <v/>
       </c>
@@ -1547,26 +2118,26 @@
       <c r="B15" t="n">
         <v>2035</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="11" t="n">
+      <c r="C15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="11">
         <f>SUM(C15:G15)</f>
         <v/>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <f>C15*1.0+D15*2.0+E15*4.0+F15*5.3+G15*7.0</f>
         <v/>
       </c>
@@ -1580,26 +2151,26 @@
       <c r="B16" t="n">
         <v>2040</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="11" t="n">
+      <c r="C16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <f>SUM(C16:G16)</f>
         <v/>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <f>C16*1.0+D16*2.0+E16*4.0+F16*5.3+G16*7.0</f>
         <v/>
       </c>
@@ -1613,26 +2184,26 @@
       <c r="B17" t="n">
         <v>2050</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="11" t="n">
+      <c r="C17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <f>SUM(C17:G17)</f>
         <v/>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="12">
         <f>C17*1.0+D17*2.0+E17*4.0+F17*5.3+G17*7.0</f>
         <v/>
       </c>
@@ -1646,26 +2217,26 @@
       <c r="B18" t="n">
         <v>2060</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="11" t="n">
+      <c r="C18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <f>SUM(C18:G18)</f>
         <v/>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <f>C18*1.0+D18*2.0+E18*4.0+F18*5.3+G18*7.0</f>
         <v/>
       </c>
@@ -1679,26 +2250,26 @@
       <c r="B19" t="n">
         <v>2070</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="11" t="n">
+      <c r="C19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="11">
         <f>SUM(C19:G19)</f>
         <v/>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="12">
         <f>C19*1.0+D19*2.0+E19*4.0+F19*5.3+G19*7.0</f>
         <v/>
       </c>
@@ -1712,26 +2283,26 @@
       <c r="B21" t="n">
         <v>2025</v>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="11" t="n">
+      <c r="C21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="11">
         <f>SUM(C21:G21)</f>
         <v/>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <f>C21*1.0+D21*2.0+E21*4.0+F21*5.3+G21*7.0</f>
         <v/>
       </c>
@@ -1745,26 +2316,26 @@
       <c r="B22" t="n">
         <v>2030</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="11" t="n">
+      <c r="C22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="11">
         <f>SUM(C22:G22)</f>
         <v/>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="12">
         <f>C22*1.0+D22*2.0+E22*4.0+F22*5.3+G22*7.0</f>
         <v/>
       </c>
@@ -1778,26 +2349,26 @@
       <c r="B23" t="n">
         <v>2035</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="11" t="n">
+      <c r="C23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="G23" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="11">
         <f>SUM(C23:G23)</f>
         <v/>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="12">
         <f>C23*1.0+D23*2.0+E23*4.0+F23*5.3+G23*7.0</f>
         <v/>
       </c>
@@ -1811,26 +2382,26 @@
       <c r="B24" t="n">
         <v>2040</v>
       </c>
-      <c r="C24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="11" t="n">
+      <c r="C24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="10" t="n">
         <v>0.55</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="11">
         <f>SUM(C24:G24)</f>
         <v/>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="12">
         <f>C24*1.0+D24*2.0+E24*4.0+F24*5.3+G24*7.0</f>
         <v/>
       </c>
@@ -1844,26 +2415,26 @@
       <c r="B25" t="n">
         <v>2050</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="11" t="n">
+      <c r="C25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="G25" s="10" t="n">
         <v>0.65</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="11">
         <f>SUM(C25:G25)</f>
         <v/>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="12">
         <f>C25*1.0+D25*2.0+E25*4.0+F25*5.3+G25*7.0</f>
         <v/>
       </c>
@@ -1877,26 +2448,26 @@
       <c r="B26" t="n">
         <v>2060</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="11" t="n">
+      <c r="C26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" s="10" t="n">
         <v>0.65</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="11">
         <f>SUM(C26:G26)</f>
         <v/>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="12">
         <f>C26*1.0+D26*2.0+E26*4.0+F26*5.3+G26*7.0</f>
         <v/>
       </c>
@@ -1910,26 +2481,26 @@
       <c r="B27" t="n">
         <v>2070</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="11" t="n">
+      <c r="C27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="G27" s="10" t="n">
         <v>0.65</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="11">
         <f>SUM(C27:G27)</f>
         <v/>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="12">
         <f>C27*1.0+D27*2.0+E27*4.0+F27*5.3+G27*7.0</f>
         <v/>
       </c>
@@ -2006,13 +2577,13 @@
       <c r="A5" t="n">
         <v>2025</v>
       </c>
-      <c r="B5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="11" t="n">
+      <c r="B5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>0.01</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="10" t="n">
         <v>0.02</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -2030,16 +2601,16 @@
       <c r="A6" t="n">
         <v>2030</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
@@ -2054,13 +2625,13 @@
       <c r="A7" t="n">
         <v>2035</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="10" t="n">
         <v>0.28</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="10" t="n">
         <v>0.55</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -2078,13 +2649,13 @@
       <c r="A8" t="n">
         <v>2040</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="10" t="n">
         <v>0.7</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -2098,13 +2669,13 @@
       <c r="A9" t="n">
         <v>2050</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="10" t="n">
         <v>0.18</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="10" t="n">
         <v>0.85</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2118,13 +2689,13 @@
       <c r="A10" t="n">
         <v>2060</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="10" t="n">
         <v>0.22</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.66</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="10" t="n">
         <v>0.88</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -2142,13 +2713,13 @@
       <c r="A11" t="n">
         <v>2070</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>0.9</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -2253,19 +2824,19 @@
           <t>Front ADAS camera</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="11" t="n">
+      <c r="C5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -2288,19 +2859,19 @@
           <t>Rear view camera</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="11" t="n">
+      <c r="E6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -2319,19 +2890,19 @@
           <t>Side / mirror cameras</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11" t="n">
+      <c r="C7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="11" t="n">
+      <c r="F7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -2354,19 +2925,19 @@
           <t>Front long-range radar</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="11" t="n">
+      <c r="C8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -2389,19 +2960,19 @@
           <t>Corner short/mid-range radars</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="11" t="n">
+      <c r="C9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="10" t="n">
         <v>0.85</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="11" t="n">
+      <c r="F9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -2424,26 +2995,26 @@
           <t>LiDAR sensor</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="C10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Driver B</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Driver B</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>DRIVER B</t>
         </is>
@@ -2463,19 +3034,19 @@
           <t>Ultrasonic sensors</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="11" t="n">
+      <c r="E11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -2494,22 +3065,22 @@
           <t>Driver monitoring camera</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="F12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
@@ -2529,19 +3100,19 @@
           <t>ADAS camera ECU (basic)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="11" t="n">
+      <c r="C13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -2564,19 +3135,19 @@
           <t>ADAS domain controller / fusion ECU</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="11" t="n">
+      <c r="C14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="F14" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="11" t="n">
+      <c r="F14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -2595,19 +3166,19 @@
           <t>Automated driving central computer</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="11" t="n">
+      <c r="C15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -2626,19 +3197,19 @@
           <t>Parking assist ECU</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="E16" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="11" t="n">
+      <c r="E16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -2649,7 +3220,7 @@
       <c r="I16" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="O18" s="15" t="inlineStr">
+      <c r="O18" s="14" t="inlineStr">
         <is>
           <t>WATCH: row 9 DECLINES as rows 10 and 11 rise - the smart camera is absorbed into the domain controller. That is a SUBSTITUTION. The static model cannot express it, and such pairs must be drawn jointly, not independently.</t>
         </is>
@@ -2755,12 +3326,12 @@
           <t>&gt;50%</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>1.6x</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>Two top-tier houses, same quantity, same year. Sets the floor for any 10-year-out forecast band.</t>
         </is>
@@ -2792,12 +3363,12 @@
           <t>4.6</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>1.20x</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>Our tier table is deliberately conservative on the late ramp.</t>
         </is>
@@ -2829,12 +3400,12 @@
           <t>15 y</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>5 y</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>Confirms +/-5 y is the right order for the Driver A band.</t>
         </is>
@@ -2866,12 +3437,12 @@
           <t>60.3 kg</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>6.9%</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Two readings of the SAME source.</t>
         </is>
@@ -2903,12 +3474,12 @@
           <t>3546 m</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>2.8%</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>A single source disagreeing WITH ITSELF. Sets the noise floor: nothing here can claim better than ~3%.</t>
         </is>
@@ -2940,12 +3511,12 @@
           <t>-44/-40/-23%</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>3-4x</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>Largest spread in the whole chain. Structural, not statistical.</t>
         </is>
@@ -2977,12 +3548,12 @@
           <t>6 / 10</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>2x</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Within normal disagreement - NOT necessarily an error.</t>
         </is>
@@ -3014,12 +3585,12 @@
           <t>0.01</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>50x</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>FAR outside every band above. This one IS an error.</t>
         </is>
@@ -3051,12 +3622,12 @@
           <t>0.90</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>3.6x</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>Genuinely unknown. Width is honest, not lazy.</t>
         </is>
@@ -3092,7 +3663,7 @@
           <t>Self-consistency floor</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>~3%</t>
         </is>
@@ -3109,7 +3680,7 @@
           <t>Cross-house forecast spread, 10 y out</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>~1.6x</t>
         </is>
@@ -3126,7 +3697,7 @@
           <t>Structural / mechanism uncertainty</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>3-4x</t>
         </is>
@@ -3143,7 +3714,7 @@
           <t>Threshold for calling something an error</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>&gt;10x</t>
         </is>
@@ -3254,8 +3825,8 @@
           <t>existing anchor</t>
         </is>
       </c>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -3283,8 +3854,8 @@
           <t>17_ / 06_</t>
         </is>
       </c>
-      <c r="F6" s="19" t="n"/>
-      <c r="G6" s="19" t="n"/>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="18" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -3312,8 +3883,8 @@
           <t>report S2.2 measured</t>
         </is>
       </c>
-      <c r="F7" s="19" t="n"/>
-      <c r="G7" s="19" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -3341,8 +3912,8 @@
           <t>report S4.1 vs Yole 2.5</t>
         </is>
       </c>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="19" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -3370,8 +3941,8 @@
           <t>report S2.4</t>
         </is>
       </c>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="19" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -3399,8 +3970,8 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="F10" s="19" t="n"/>
-      <c r="G10" s="19" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -3428,8 +3999,8 @@
           <t>report S6.3</t>
         </is>
       </c>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="19" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -3457,8 +4028,8 @@
           <t>interface doc S1</t>
         </is>
       </c>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -3486,8 +4057,8 @@
           <t>report S7.2</t>
         </is>
       </c>
-      <c r="F13" s="19" t="n"/>
-      <c r="G13" s="19" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -3515,8 +4086,264 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="19" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>One physical box = one harness drop. One element = one chip inside it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>06_ enumerates ELEMENTS -- a corner radar appears twice, as an RF transceiver and as a temperature sensor. The wiring model needs MODULES: a radar box takes ONE cable however many chips are inside. PRIMARY is the element whose count equals the module count; the companions ride along in the same box and must never be counted as separate wiring endpoints. Rows with PRIMARY '-' are ECUs, not sensor modules -- their elements are inputs from other modules and are a KNOWN DOUBLE-COUNT RISK (see 06_ sheet Notes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>PRIMARY element (= module count)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Companion elements</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Elements per module</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Front ADAS camera</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>CMOS image sensor</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>temperature sensor</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Rear view camera</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>CMOS image sensor</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Side / mirror cameras</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>CMOS image sensor</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Front long-range radar</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>RF transceiver</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>temperature sensor</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Corner short/mid-range radars</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>RF transceiver</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>temperature sensor</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>LiDAR sensor</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>laser diode array</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>photodetector array, IMU, temperature sensor</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Ultrasonic sensors</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>ultrasonic transducer</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Driver monitoring camera</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>IR camera sensor</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>IR LED array</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>ADAS camera ECU (basic)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>CMOS image sensor, temperature sensor</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Parking assist ECU</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>ultrasonic sensor, camera input</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/19_ADAS_sensor_adoption.xlsx
+++ b/Data/19_ADAS_sensor_adoption.xlsx
@@ -2293,10 +2293,10 @@
         <v>0.25</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="H21" s="11">
         <f>SUM(C21:G21)</f>
@@ -2326,10 +2326,10 @@
         <v>0.15</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H22" s="11">
         <f>SUM(C22:G22)</f>
